--- a/selenium_tests/selenium_test_report.xlsx
+++ b/selenium_tests/selenium_test_report.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -92,13 +92,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H326"/>
+  <dimension ref="A1:F326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -474,8 +468,6 @@
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -509,16 +501,6 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Execution Time (ms)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -551,14 +533,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -591,14 +565,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -631,14 +597,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -671,14 +629,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -711,14 +661,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -751,14 +693,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -791,14 +725,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -831,14 +757,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -871,14 +789,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -911,14 +821,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -951,14 +853,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -991,14 +885,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1031,14 +917,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1071,14 +949,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1111,14 +981,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>1271</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1151,14 +1013,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1191,14 +1045,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -1231,14 +1077,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1271,14 +1109,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -1311,14 +1141,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1351,14 +1173,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -1391,14 +1205,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>422</v>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1431,14 +1237,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>707</v>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -1471,14 +1269,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1511,14 +1301,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>1087</v>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -1551,14 +1333,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>406</v>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1591,14 +1365,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -1631,14 +1397,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -1671,14 +1429,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -1711,14 +1461,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -1751,14 +1493,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
-        <v>1454</v>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -1791,14 +1525,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -1831,14 +1557,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -1871,14 +1589,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -1911,14 +1621,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -1951,14 +1653,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -1991,14 +1685,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -2031,14 +1717,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -2071,14 +1749,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -2111,14 +1781,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2151,14 +1813,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -2191,14 +1845,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -2231,14 +1877,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -2271,14 +1909,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -2311,14 +1941,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -2351,14 +1973,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
-        <v>629</v>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -2391,14 +2005,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -2431,14 +2037,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -2471,14 +2069,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -2511,14 +2101,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -2551,14 +2133,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
@@ -2591,14 +2165,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -2631,14 +2197,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
@@ -2671,14 +2229,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -2711,14 +2261,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -2751,14 +2293,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -2791,14 +2325,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -2831,14 +2357,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -2871,14 +2389,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -2911,14 +2421,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -2951,14 +2453,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
@@ -2991,14 +2485,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -3031,14 +2517,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -3071,14 +2549,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
-        <v>1238</v>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -3111,14 +2581,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
-        <v>1223</v>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -3151,14 +2613,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -3191,14 +2645,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
@@ -3231,14 +2677,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -3271,14 +2709,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -3311,14 +2741,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -3351,14 +2773,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
@@ -3391,14 +2805,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -3431,14 +2837,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
@@ -3471,14 +2869,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -3511,14 +2901,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
@@ -3551,14 +2933,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -3591,14 +2965,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
@@ -3631,14 +2997,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -3671,14 +3029,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
@@ -3711,14 +3061,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -3751,14 +3093,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
@@ -3791,14 +3125,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -3831,14 +3157,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
@@ -3871,14 +3189,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -3911,14 +3221,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
@@ -3951,14 +3253,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -3991,14 +3285,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
@@ -4031,14 +3317,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -4071,14 +3349,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
@@ -4111,14 +3381,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -4151,14 +3413,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
@@ -4191,14 +3445,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -4231,14 +3477,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
@@ -4271,14 +3509,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -4311,14 +3541,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
@@ -4351,14 +3573,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -4391,14 +3605,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
@@ -4431,14 +3637,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="100" ht="24" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -4471,14 +3669,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
@@ -4511,14 +3701,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -4551,14 +3733,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="H102" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
@@ -4591,14 +3765,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -4631,14 +3797,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="H104" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
@@ -4671,14 +3829,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="H105" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -4711,14 +3861,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="H106" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
@@ -4751,14 +3893,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="H107" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -4791,14 +3925,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H108" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
@@ -4831,14 +3957,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -4871,14 +3989,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="H110" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
@@ -4911,14 +4021,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -4951,14 +4053,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="H112" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
@@ -4991,14 +4085,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -5031,14 +4117,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="H114" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="115" ht="24" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
@@ -5071,14 +4149,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="H115" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -5111,14 +4181,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
@@ -5151,14 +4213,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H117" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -5191,14 +4245,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="H118" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
@@ -5231,14 +4277,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="H119" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="120" ht="24" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -5271,14 +4309,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="H120" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
@@ -5311,14 +4341,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="H121" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -5351,14 +4373,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="H122" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
@@ -5391,14 +4405,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="H123" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -5431,14 +4437,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
-        <v>1463</v>
-      </c>
-      <c r="H124" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="125" ht="24" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
@@ -5471,14 +4469,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
-        <v>595</v>
-      </c>
-      <c r="H125" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -5511,14 +4501,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
-        <v>873</v>
-      </c>
-      <c r="H126" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
@@ -5551,14 +4533,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
-        <v>1304</v>
-      </c>
-      <c r="H127" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="128" ht="24" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -5591,14 +4565,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="129" ht="24" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
@@ -5631,14 +4597,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="H129" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="130" ht="24" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -5671,14 +4629,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="H130" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
@@ -5711,14 +4661,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="H131" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="132" ht="24" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
@@ -5751,14 +4693,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="H132" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="133" ht="24" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
@@ -5791,14 +4725,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="H133" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -5831,14 +4757,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="135" ht="24" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
@@ -5871,14 +4789,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="H135" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="136" ht="24" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
@@ -5911,14 +4821,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="137" ht="24" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
@@ -5951,14 +4853,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="H137" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="138" ht="24" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
@@ -5991,14 +4885,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="H138" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
@@ -6031,14 +4917,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="140" ht="24" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
@@ -6071,14 +4949,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="141" ht="24" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
@@ -6111,14 +4981,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="H141" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="142" ht="24" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
@@ -6151,14 +5013,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H142" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="143" ht="24" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
@@ -6191,14 +5045,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="H143" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="144" ht="24" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
@@ -6231,14 +5077,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H144" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="145" ht="24" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
@@ -6271,14 +5109,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
-        <v>896</v>
-      </c>
-      <c r="H145" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="146" ht="24" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -6311,14 +5141,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="H146" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="147" ht="24" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
@@ -6351,14 +5173,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="H147" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="148" ht="24" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
@@ -6391,14 +5205,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H148" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="149" ht="24" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
@@ -6431,14 +5237,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H149" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="150" ht="24" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
@@ -6471,14 +5269,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H150" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="151" ht="24" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
@@ -6511,14 +5301,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="H151" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="152" ht="24" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
@@ -6551,14 +5333,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="H152" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="153" ht="24" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
@@ -6591,14 +5365,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="H153" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="154" ht="24" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
@@ -6631,14 +5397,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="H154" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="155" ht="24" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
@@ -6671,14 +5429,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="H155" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="156" ht="24" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
@@ -6711,14 +5461,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="H156" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="157" ht="24" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
@@ -6751,14 +5493,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="H157" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="158" ht="24" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -6791,14 +5525,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H158" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="159" ht="24" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
@@ -6831,14 +5557,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="H159" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="160" ht="24" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
@@ -6871,14 +5589,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="H160" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="161" ht="24" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
@@ -6911,14 +5621,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H161" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="162" ht="24" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
@@ -6951,14 +5653,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
-        <v>109</v>
-      </c>
-      <c r="H162" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="163" ht="24" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
@@ -6991,14 +5685,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
-        <v>1192</v>
-      </c>
-      <c r="H163" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="164" ht="24" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
@@ -7031,14 +5717,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="H164" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="165" ht="24" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
@@ -7071,14 +5749,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H165" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="166" ht="24" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
@@ -7111,14 +5781,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="H166" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="167" ht="24" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
@@ -7151,14 +5813,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H167" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="168" ht="24" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
@@ -7191,14 +5845,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="H168" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="169" ht="24" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
@@ -7231,14 +5877,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H169" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="170" ht="24" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
@@ -7271,14 +5909,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="H170" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="171" ht="24" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
@@ -7311,14 +5941,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="H171" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="172" ht="24" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
@@ -7351,14 +5973,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H172" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="173" ht="24" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
@@ -7391,14 +6005,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H173" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="174" ht="24" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
@@ -7431,14 +6037,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H174" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="175" ht="24" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
@@ -7471,14 +6069,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H175" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="176" ht="24" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
@@ -7511,14 +6101,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="H176" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="177" ht="24" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
@@ -7551,14 +6133,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="H177" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="178" ht="24" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
@@ -7591,14 +6165,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="H178" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="179" ht="24" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
@@ -7631,14 +6197,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="H179" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="180" ht="24" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
@@ -7671,14 +6229,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="H180" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="181" ht="24" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
@@ -7711,14 +6261,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
-        <v>890</v>
-      </c>
-      <c r="H181" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="182" ht="24" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
@@ -7751,14 +6293,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="H182" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="183" ht="24" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
@@ -7791,14 +6325,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="H183" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="184" ht="24" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
@@ -7831,14 +6357,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="H184" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="185" ht="24" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
@@ -7871,14 +6389,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="H185" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="186" ht="24" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -7911,14 +6421,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="H186" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="187" ht="24" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
@@ -7951,14 +6453,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="H187" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="188" ht="24" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
@@ -7991,14 +6485,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="H188" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="189" ht="24" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
@@ -8031,14 +6517,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="H189" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="190" ht="24" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
@@ -8071,14 +6549,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="H190" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="191" ht="24" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
@@ -8111,14 +6581,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="H191" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="192" ht="24" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
@@ -8151,14 +6613,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="H192" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="193" ht="24" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
@@ -8191,14 +6645,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="H193" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="194" ht="24" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
@@ -8231,14 +6677,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="H194" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="195" ht="24" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
@@ -8271,14 +6709,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="H195" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="196" ht="24" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
@@ -8311,14 +6741,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="H196" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="197" ht="24" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
@@ -8351,14 +6773,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="H197" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="198" ht="24" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
@@ -8391,14 +6805,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="H198" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="199" ht="24" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
@@ -8431,14 +6837,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="H199" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="200" ht="24" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
@@ -8471,14 +6869,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="H200" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="201" ht="24" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
@@ -8511,24 +6901,16 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="H201" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="202" ht="24" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>TC-105</t>
+          <t>TC-099</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Cases Active Style Highlight</t>
+          <t>Accessibility Skip Navigation Link</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -8538,37 +6920,29 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Cases Active Style Highlight</t>
+          <t>Accessibility Skip Navigation Link</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Cases' shows active color background highlight when selected.</t>
+          <t>Verify skip navigation anchor is present as first focusable element.</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G202" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="H202" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="203" ht="24" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>TC-104</t>
+          <t>TC-076</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Cases Icon Render</t>
+          <t>Active Nav Tab Styling Indicator</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -8578,37 +6952,29 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Cases Icon Render</t>
+          <t>Active Nav Tab Styling Indicator</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Verify correct Lucide icon renders for 'Cases' on sidebar layout.</t>
+          <t>Verify active menu item displays distinct blue tag border highlight.</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G203" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="H203" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="204" ht="24" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>TC-106</t>
+          <t>TC-107</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Cases Mobile Viewport Wrap</t>
+          <t>Active Page Logo Reload Prevention</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -8618,37 +6984,29 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Cases Mobile Viewport Wrap</t>
+          <t>Active Page Logo Reload Prevention</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Cases' wraps or shifts to bottom tab bar on mobile viewport widths.</t>
+          <t>Verify clicking active page link in menu does not trigger browser reload.</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G204" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="H204" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="205" ht="24" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>TC-103</t>
+          <t>TC-115</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Cases Navigation Link</t>
+          <t>Active Style Removal on Navigation</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -8658,37 +7016,29 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Cases Navigation Link</t>
+          <t>Active Style Removal on Navigation</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the 'Cases' tab routes to correct URL path endpoint.</t>
+          <t>Verify active menu styling leaves tab when navigating away.</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G205" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H205" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="206" ht="24" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>TC-107</t>
+          <t>TC-113</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Cases Sidebar Layout Alignment</t>
+          <t>Avatar Action History Prevention</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -8698,37 +7048,29 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Cases Sidebar Layout Alignment</t>
+          <t>Avatar Action History Prevention</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Cases' aligns nicely in desktop sidebar vertical navigation stack.</t>
+          <t>Verify navigation via settings dropdown does not record duplicate back loops.</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G206" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="H206" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="207" ht="24" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>TC-108</t>
+          <t>TC-112</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Cases Test ID Selector</t>
+          <t>Base Layout Typography System</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -8738,37 +7080,29 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Cases Test ID Selector</t>
+          <t>Base Layout Typography System</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Cases' element has a unique accessibility identifier or test ID.</t>
+          <t>Verify all navigation components load standardized font families.</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="H207" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="208" ht="24" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>TC-099</t>
+          <t>TC-085</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Doctors Active Style Highlight</t>
+          <t>Browser Back History Navigation</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -8778,37 +7112,29 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Doctors Active Style Highlight</t>
+          <t>Browser Back History Navigation</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Doctors' shows active color background highlight when selected.</t>
+          <t>Verify clicking browser back button loads previous layout safely.</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G208" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="H208" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="209" ht="24" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>TC-098</t>
+          <t>TC-086</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Doctors Icon Render</t>
+          <t>Browser Forward History Navigation</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -8818,37 +7144,29 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Doctors Icon Render</t>
+          <t>Browser Forward History Navigation</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Verify correct Lucide icon renders for 'Doctors' on sidebar layout.</t>
+          <t>Verify clicking browser forward button restores navigated views.</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G209" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H209" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="210" ht="24" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>TC-100</t>
+          <t>TC-068</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Doctors Mobile Viewport Wrap</t>
+          <t>Cases Admin History Link</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -8858,37 +7176,29 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Doctors Mobile Viewport Wrap</t>
+          <t>Cases Admin History Link</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Doctors' wraps or shifts to bottom tab bar on mobile viewport widths.</t>
+          <t>Verify clicking the 'Cases' link routes to global cases archive list.</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G210" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H210" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="211" ht="24" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>TC-097</t>
+          <t>TC-075</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Doctors Navigation Link</t>
+          <t>Collapsed Sidebar Tooltip Popup</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -8898,37 +7208,29 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Doctors Navigation Link</t>
+          <t>Collapsed Sidebar Tooltip Popup</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the 'Doctors' tab routes to correct URL path endpoint.</t>
+          <t>Verify hovering collapsed icons displays popover context tooltip.</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G211" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="H211" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="212" ht="24" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>TC-101</t>
+          <t>TC-061</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Doctors Sidebar Layout Alignment</t>
+          <t>Dashboard Home Link</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -8938,37 +7240,29 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Doctors Sidebar Layout Alignment</t>
+          <t>Dashboard Home Link</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Doctors' aligns nicely in desktop sidebar vertical navigation stack.</t>
+          <t>Verify clicking the 'Home' link routes to the clinician dashboard.</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G212" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H212" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="213" ht="24" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>TC-102</t>
+          <t>TC-079</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Doctors Test ID Selector</t>
+          <t>Default OS Theme Match Logic</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -8978,37 +7272,29 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Doctors Test ID Selector</t>
+          <t>Default OS Theme Match Logic</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Doctors' element has a unique accessibility identifier or test ID.</t>
+          <t>Verify layout matching system OS preferences if local storage is blank.</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G213" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="H213" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="214" ht="24" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>TC-063</t>
+          <t>TC-067</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Active Style Highlight</t>
+          <t>Doctors Directory Link</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9018,37 +7304,29 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Active Style Highlight</t>
+          <t>Doctors Directory Link</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Home / Dashboard' shows active color background highlight when selected.</t>
+          <t>Verify clicking the 'Doctors' link routes to the medical staff database table.</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G214" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="H214" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="215" ht="24" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>TC-062</t>
+          <t>TC-103</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Icon Render</t>
+          <t>Document Title Sync on Routing</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -9058,37 +7336,29 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Icon Render</t>
+          <t>Document Title Sync on Routing</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Verify correct Lucide icon renders for 'Home / Dashboard' on sidebar layout.</t>
+          <t>Verify browser document title tag updates on route change.</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G215" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="H215" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="216" ht="24" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>TC-064</t>
+          <t>TC-092</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Mobile Viewport Wrap</t>
+          <t>Dropdown Navigation Settings Link</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -9098,37 +7368,29 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Mobile Viewport Wrap</t>
+          <t>Dropdown Navigation Settings Link</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Home / Dashboard' wraps or shifts to bottom tab bar on mobile viewport widths.</t>
+          <t>Verify clicking 'Account Settings' in dropdown routes to settings.</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G216" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="H216" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="217" ht="24" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>TC-061</t>
+          <t>TC-117</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Navigation Link</t>
+          <t>Footer Copyright Current Year Match</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -9138,37 +7400,29 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Navigation Link</t>
+          <t>Footer Copyright Current Year Match</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the 'Home / Dashboard' tab routes to correct URL path endpoint.</t>
+          <t>Verify footer copyright text displays active current year.</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G217" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="H217" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="218" ht="24" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>TC-065</t>
+          <t>TC-090</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Sidebar Layout Alignment</t>
+          <t>Header Account Settings Dropdown</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9178,37 +7432,29 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Sidebar Layout Alignment</t>
+          <t>Header Account Settings Dropdown</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Home / Dashboard' aligns nicely in desktop sidebar vertical navigation stack.</t>
+          <t>Verify clicking avatar opens settings actions context menu.</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G218" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="H218" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="219" ht="24" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>TC-066</t>
+          <t>TC-080</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Test ID Selector</t>
+          <t>Header Breadcrumb Navigation Text</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9218,37 +7464,29 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Home / Dashboard Test ID Selector</t>
+          <t>Header Breadcrumb Navigation Text</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Home / Dashboard' element has a unique accessibility identifier or test ID.</t>
+          <t>Verify page navigation path header updates dynamically on routing.</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G219" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H219" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="220" ht="24" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>TC-087</t>
+          <t>TC-082</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Insights Active Style Highlight</t>
+          <t>Header Notification Drawer Close</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9258,37 +7496,29 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Insights Active Style Highlight</t>
+          <t>Header Notification Drawer Close</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Insights' shows active color background highlight when selected.</t>
+          <t>Verify clicking overlay backdrop dismisses sliding alert drawer.</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G220" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="H220" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="221" ht="24" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>TC-086</t>
+          <t>TC-119</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Insights Icon Render</t>
+          <t>Header Notification Drawer Max Height</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -9298,37 +7528,29 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Insights Icon Render</t>
+          <t>Header Notification Drawer Max Height</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Verify correct Lucide icon renders for 'Insights' on sidebar layout.</t>
+          <t>Verify notification dropdown list height is capped at max 400px.</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G221" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="H221" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="222" ht="24" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>TC-088</t>
+          <t>TC-081</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Insights Mobile Viewport Wrap</t>
+          <t>Header Notification Drawer Open</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -9338,37 +7560,29 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Insights Mobile Viewport Wrap</t>
+          <t>Header Notification Drawer Open</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Insights' wraps or shifts to bottom tab bar on mobile viewport widths.</t>
+          <t>Verify clicking notification bell opens sliding alert drawer.</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G222" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="H222" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="223" ht="24" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>TC-085</t>
+          <t>TC-083</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Insights Navigation Link</t>
+          <t>Header Notification Unread Badge</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -9378,37 +7592,29 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Insights Navigation Link</t>
+          <t>Header Notification Unread Badge</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the 'Insights' tab routes to correct URL path endpoint.</t>
+          <t>Verify red badge counter on bell represents unread alerts.</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G223" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="H223" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="224" ht="24" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>TC-089</t>
+          <t>TC-111</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Insights Sidebar Layout Alignment</t>
+          <t>Header Shadow Scroll Activation</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -9418,37 +7624,29 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Insights Sidebar Layout Alignment</t>
+          <t>Header Shadow Scroll Activation</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Insights' aligns nicely in desktop sidebar vertical navigation stack.</t>
+          <t>Verify header shadow becomes denser when scrolling page down.</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G224" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="H224" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="225" ht="24" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>TC-090</t>
+          <t>TC-065</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Insights Test ID Selector</t>
+          <t>Insights Metrics Link</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -9458,37 +7656,29 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Insights Test ID Selector</t>
+          <t>Insights Metrics Link</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Insights' element has a unique accessibility identifier or test ID.</t>
+          <t>Verify clicking the 'Insights' link routes to clinical guide analytics page.</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G225" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="H225" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="226" ht="24" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>TC-069</t>
+          <t>TC-087</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>New Case Active Style Highlight</t>
+          <t>Invalid Path Route Redirection</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -9498,37 +7688,29 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>New Case Active Style Highlight</t>
+          <t>Invalid Path Route Redirection</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Verify 'New Case' shows active color background highlight when selected.</t>
+          <t>Verify typing non-existent URL routes user to 404 page.</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G226" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H226" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="227" ht="24" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>TC-068</t>
+          <t>TC-098</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>New Case Icon Render</t>
+          <t>Keyboard Enter Key Routing Trigger</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -9538,37 +7720,29 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>New Case Icon Render</t>
+          <t>Keyboard Enter Key Routing Trigger</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Verify correct Lucide icon renders for 'New Case' on sidebar layout.</t>
+          <t>Verify pressing Enter key on focused navigation link routes user.</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G227" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H227" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="228" ht="24" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>TC-070</t>
+          <t>TC-097</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>New Case Mobile Viewport Wrap</t>
+          <t>Keyboard Navigation Tab Index Rings</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -9578,37 +7752,29 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>New Case Mobile Viewport Wrap</t>
+          <t>Keyboard Navigation Tab Index Rings</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Verify 'New Case' wraps or shifts to bottom tab bar on mobile viewport widths.</t>
+          <t>Verify interactive navigation links show blue ring outlines on Tab.</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G228" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="H228" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="229" ht="24" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>TC-067</t>
+          <t>TC-116</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>New Case Navigation Link</t>
+          <t>Landscape Tablet Viewport Header Stacking</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -9618,37 +7784,29 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>New Case Navigation Link</t>
+          <t>Landscape Tablet Viewport Header Stacking</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the 'New Case' tab routes to correct URL path endpoint.</t>
+          <t>Verify header options layout stacks cleanly on landscape tablet widths.</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G229" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="H229" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="230" ht="24" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>TC-071</t>
+          <t>TC-105</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>New Case Sidebar Layout Alignment</t>
+          <t>Main Content Sticky Sidebar Scroll</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -9658,37 +7816,29 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>New Case Sidebar Layout Alignment</t>
+          <t>Main Content Sticky Sidebar Scroll</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Verify 'New Case' aligns nicely in desktop sidebar vertical navigation stack.</t>
+          <t>Verify sidebar remains locked in viewport during main window scrolls.</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G230" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="H230" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="231" ht="24" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>TC-072</t>
+          <t>TC-093</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>New Case Test ID Selector</t>
+          <t>Mobile Responsive Bottom Navigation</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -9698,37 +7848,29 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>New Case Test ID Selector</t>
+          <t>Mobile Responsive Bottom Navigation</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Verify 'New Case' element has a unique accessibility identifier or test ID.</t>
+          <t>Verify bottom navigation bar renders on viewports under 480px.</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G231" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="H231" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="232" ht="24" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>TC-093</t>
+          <t>TC-094</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Overview Active Style Highlight</t>
+          <t>Mobile Responsive Slider Drawer</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -9738,37 +7880,29 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Overview Active Style Highlight</t>
+          <t>Mobile Responsive Slider Drawer</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Overview' shows active color background highlight when selected.</t>
+          <t>Verify navigation menu loads as slide-out drawer on viewports under 768px.</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G232" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H232" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="233" ht="24" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>TC-092</t>
+          <t>TC-096</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Overview Icon Render</t>
+          <t>Mobile Slider Drawer Close Button</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -9778,37 +7912,29 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Overview Icon Render</t>
+          <t>Mobile Slider Drawer Close Button</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>Verify correct Lucide icon renders for 'Overview' on sidebar layout.</t>
+          <t>Verify clicking 'X' inside slide-out drawer hides navigation menu.</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G233" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H233" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="234" ht="24" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>TC-094</t>
+          <t>TC-095</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Overview Mobile Viewport Wrap</t>
+          <t>Mobile Swipe Gesture Sidebar Drawer</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -9818,37 +7944,29 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Overview Mobile Viewport Wrap</t>
+          <t>Mobile Swipe Gesture Sidebar Drawer</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Overview' wraps or shifts to bottom tab bar on mobile viewport widths.</t>
+          <t>Verify swipe gesture from screen edge pulls drawer menu into view.</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G234" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H234" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="235" ht="24" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>TC-091</t>
+          <t>TC-074</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Overview Navigation Link</t>
+          <t>Navigation Items Hover Background</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -9858,37 +7976,29 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Overview Navigation Link</t>
+          <t>Navigation Items Hover Background</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the 'Overview' tab routes to correct URL path endpoint.</t>
+          <t>Verify cursor hover triggers background color transition on nav items.</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G235" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="H235" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="236" ht="24" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>TC-095</t>
+          <t>TC-062</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Overview Sidebar Layout Alignment</t>
+          <t>New Case Form Link</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -9898,37 +8008,29 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Overview Sidebar Layout Alignment</t>
+          <t>New Case Form Link</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Overview' aligns nicely in desktop sidebar vertical navigation stack.</t>
+          <t>Verify clicking the 'New Case' link routes to the patient intake form.</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G236" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="H236" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="237" ht="24" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>TC-096</t>
+          <t>TC-088</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Overview Test ID Selector</t>
+          <t>NotFound View Return Action</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -9938,37 +8040,29 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Overview Test ID Selector</t>
+          <t>NotFound View Return Action</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Overview' element has a unique accessibility identifier or test ID.</t>
+          <t>Verify clicking 'Go Back Home' button on 404 routes back to home.</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G237" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="H237" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="238" ht="24" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>TC-075</t>
+          <t>TC-109</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Procedures Active Style Highlight</t>
+          <t>Notification Drawer Click Action</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -9978,37 +8072,29 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Procedures Active Style Highlight</t>
+          <t>Notification Drawer Click Action</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Procedures' shows active color background highlight when selected.</t>
+          <t>Verify clicking notification row opens corresponding case record.</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G238" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="H238" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="239" ht="24" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>TC-074</t>
+          <t>TC-108</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Procedures Icon Render</t>
+          <t>Notification Drawer Timestamps</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -10018,37 +8104,29 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Procedures Icon Render</t>
+          <t>Notification Drawer Timestamps</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Verify correct Lucide icon renders for 'Procedures' on sidebar layout.</t>
+          <t>Verify notifications show human-readable relative time strings.</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G239" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="H239" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="240" ht="24" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>TC-076</t>
+          <t>TC-066</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Procedures Mobile Viewport Wrap</t>
+          <t>Overview Org Link</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -10058,37 +8136,29 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Procedures Mobile Viewport Wrap</t>
+          <t>Overview Org Link</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Procedures' wraps or shifts to bottom tab bar on mobile viewport widths.</t>
+          <t>Verify clicking the 'Overview' link routes to organizational overview stats.</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G240" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="H240" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="241" ht="24" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>TC-073</t>
+          <t>TC-063</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Procedures Navigation Link</t>
+          <t>Procedures Library Link</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -10098,37 +8168,29 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Procedures Navigation Link</t>
+          <t>Procedures Library Link</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the 'Procedures' tab routes to correct URL path endpoint.</t>
+          <t>Verify clicking the 'Procedures' link routes to the checklist catalog.</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G241" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="H241" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="242" ht="24" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>TC-077</t>
+          <t>TC-091</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Procedures Sidebar Layout Alignment</t>
+          <t>Profile Dropdown Area Dismissal</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -10138,37 +8200,29 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Procedures Sidebar Layout Alignment</t>
+          <t>Profile Dropdown Area Dismissal</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Procedures' aligns nicely in desktop sidebar vertical navigation stack.</t>
+          <t>Verify clicking outside dropdown closes accounts menu.</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G242" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="H242" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="243" ht="24" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>TC-078</t>
+          <t>TC-064</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Procedures Test ID Selector</t>
+          <t>Records Archive Link</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10178,37 +8232,29 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Procedures Test ID Selector</t>
+          <t>Records Archive Link</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Procedures' element has a unique accessibility identifier or test ID.</t>
+          <t>Verify clicking the 'Records' link routes to historical patient files list.</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G243" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H243" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="244" ht="24" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>TC-081</t>
+          <t>TC-069</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Records Active Style Highlight</t>
+          <t>Reports Center Link</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10218,37 +8264,29 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Records Active Style Highlight</t>
+          <t>Reports Center Link</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Records' shows active color background highlight when selected.</t>
+          <t>Verify clicking the 'Reports' link routes to summary download center.</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G244" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="H244" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="245" ht="24" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>TC-080</t>
+          <t>TC-106</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Records Icon Render</t>
+          <t>Sidebar Brand Title Header Match</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -10258,37 +8296,29 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Records Icon Render</t>
+          <t>Sidebar Brand Title Header Match</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Verify correct Lucide icon renders for 'Records' on sidebar layout.</t>
+          <t>Verify sidebar header title shows name matching user organization.</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G245" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="H245" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="246" ht="24" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>TC-082</t>
+          <t>TC-072</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Records Mobile Viewport Wrap</t>
+          <t>Sidebar Collapse Toggle Button</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -10298,37 +8328,29 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Records Mobile Viewport Wrap</t>
+          <t>Sidebar Collapse Toggle Button</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Records' wraps or shifts to bottom tab bar on mobile viewport widths.</t>
+          <t>Verify clicking the collapse arrow shrinks sidebar width.</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G246" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H246" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="247" ht="24" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>TC-079</t>
+          <t>TC-110</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Records Navigation Link</t>
+          <t>Sidebar Custom Scrollbar Styles</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10338,37 +8360,29 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Records Navigation Link</t>
+          <t>Sidebar Custom Scrollbar Styles</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the 'Records' tab routes to correct URL path endpoint.</t>
+          <t>Verify scrollbar element within sidebar matches theme palette.</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G247" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="H247" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="248" ht="24" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>TC-083</t>
+          <t>TC-073</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Records Sidebar Layout Alignment</t>
+          <t>Sidebar Expand Toggle Button</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10378,37 +8392,29 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Records Sidebar Layout Alignment</t>
+          <t>Sidebar Expand Toggle Button</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Records' aligns nicely in desktop sidebar vertical navigation stack.</t>
+          <t>Verify clicking the expand arrow on collapsed sidebar restores width.</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G248" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="H248" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="249" ht="24" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>TC-084</t>
+          <t>TC-101</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Records Test ID Selector</t>
+          <t>Sidebar Footer Help Center Link</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -10418,37 +8424,29 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Records Test ID Selector</t>
+          <t>Sidebar Footer Help Center Link</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Records' element has a unique accessibility identifier or test ID.</t>
+          <t>Verify clicking 'Help Center' opens external user documentation.</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G249" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H249" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="250" ht="24" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>TC-111</t>
+          <t>TC-100</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Reports Active Style Highlight</t>
+          <t>Sidebar Footer Support Link Display</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -10458,37 +8456,29 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Reports Active Style Highlight</t>
+          <t>Sidebar Footer Support Link Display</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Reports' shows active color background highlight when selected.</t>
+          <t>Verify footer 'Contact Support' link displays at bottom of sidebar.</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G250" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="H250" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="251" ht="24" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>TC-110</t>
+          <t>TC-071</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Reports Icon Render</t>
+          <t>Sidebar Header Logo Action</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -10498,37 +8488,29 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Reports Icon Render</t>
+          <t>Sidebar Header Logo Action</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>Verify correct Lucide icon renders for 'Reports' on sidebar layout.</t>
+          <t>Verify clicking the branding logo in sidebar header routes user to home.</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G251" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H251" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="252" ht="24" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>TC-112</t>
+          <t>TC-114</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Reports Mobile Viewport Wrap</t>
+          <t>Subpage Logo Header Home Route</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -10538,37 +8520,29 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Reports Mobile Viewport Wrap</t>
+          <t>Subpage Logo Header Home Route</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Reports' wraps or shifts to bottom tab bar on mobile viewport widths.</t>
+          <t>Verify clicking header logo from sub-pages routes user back home.</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G252" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="H252" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="253" ht="24" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>TC-109</t>
+          <t>TC-078</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Reports Navigation Link</t>
+          <t>Theme Choice Local Storage Cache</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -10578,37 +8552,29 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Reports Navigation Link</t>
+          <t>Theme Choice Local Storage Cache</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the 'Reports' tab routes to correct URL path endpoint.</t>
+          <t>Verify selected theme preference is cached in browser local storage.</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G253" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H253" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="254" ht="24" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>TC-113</t>
+          <t>TC-070</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Reports Sidebar Layout Alignment</t>
+          <t>Theme Style Mode Switcher</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -10618,37 +8584,29 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Reports Sidebar Layout Alignment</t>
+          <t>Theme Style Mode Switcher</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Reports' aligns nicely in desktop sidebar vertical navigation stack.</t>
+          <t>Verify clicking the theme toggle changes active layout visual styling.</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G254" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="H254" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="255" ht="24" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>TC-114</t>
+          <t>TC-077</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Reports Test ID Selector</t>
+          <t>Theme Toggle Sun Moon Icons</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -10658,37 +8616,29 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Reports Test ID Selector</t>
+          <t>Theme Toggle Sun Moon Icons</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Reports' element has a unique accessibility identifier or test ID.</t>
+          <t>Verify theme toggle button switches graphic illustration on click.</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G255" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="H255" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="256" ht="24" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>TC-117</t>
+          <t>TC-104</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Active Style Highlight</t>
+          <t>Top Routing Loading Bar Indicator</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -10698,37 +8648,29 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Active Style Highlight</t>
+          <t>Top Routing Loading Bar Indicator</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Theme Toggle' shows active color background highlight when selected.</t>
+          <t>Verify top loading bar strip display during page transition times.</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G256" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="H256" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="257" ht="24" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>TC-116</t>
+          <t>TC-084</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Icon Render</t>
+          <t>Unauthorized Navigation Guard Redirect</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -10738,37 +8680,29 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Icon Render</t>
+          <t>Unauthorized Navigation Guard Redirect</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>Verify correct Lucide icon renders for 'Theme Toggle' on sidebar layout.</t>
+          <t>Verify deleting local session token forces redirect back to login.</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G257" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H257" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="258" ht="24" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>TC-118</t>
+          <t>TC-089</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Mobile Viewport Wrap</t>
+          <t>User Profile Avatar Letter Check</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -10778,37 +8712,29 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Mobile Viewport Wrap</t>
+          <t>User Profile Avatar Letter Check</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Theme Toggle' wraps or shifts to bottom tab bar on mobile viewport widths.</t>
+          <t>Verify header avatar shows first letter of user profile name.</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G258" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="H258" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="259" ht="24" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>TC-115</t>
+          <t>TC-118</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Navigation Link</t>
+          <t>User Role Label Subheader Text</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -10818,37 +8744,29 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Navigation Link</t>
+          <t>User Role Label Subheader Text</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the 'Theme Toggle' tab routes to correct URL path endpoint.</t>
+          <t>Verify user profile role label displays in sidebar header.</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G259" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="H259" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="260" ht="24" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>TC-119</t>
+          <t>TC-120</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Sidebar Layout Alignment</t>
+          <t>WebSocket Connection Offline Banner</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -10858,37 +8776,29 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Sidebar Layout Alignment</t>
+          <t>WebSocket Connection Offline Banner</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Theme Toggle' aligns nicely in desktop sidebar vertical navigation stack.</t>
+          <t>Verify warning banner appears when WebSockets lose network link.</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G260" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="H260" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
     <row r="261" ht="24" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>TC-120</t>
+          <t>TC-102</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Test ID Selector</t>
+          <t>Workspace Container Padding Buffer</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -10898,25 +8808,17 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Theme Toggle Test ID Selector</t>
+          <t>Workspace Container Padding Buffer</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Theme Toggle' element has a unique accessibility identifier or test ID.</t>
+          <t>Verify main content layout maintains padding buffer to avoid sidebar overlap.</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G261" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="H261" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
@@ -10951,14 +8853,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="H262" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="263" ht="24" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
@@ -10991,14 +8885,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="H263" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="264" ht="24" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
@@ -11031,14 +8917,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="H264" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="265" ht="24" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
@@ -11071,14 +8949,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
-        <v>608</v>
-      </c>
-      <c r="H265" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="266" ht="24" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
@@ -11111,14 +8981,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
-        <v>171</v>
-      </c>
-      <c r="H266" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="267" ht="24" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
@@ -11151,14 +9013,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
-        <v>1481</v>
-      </c>
-      <c r="H267" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="268" ht="24" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
@@ -11191,14 +9045,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="H268" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="269" ht="24" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
@@ -11231,14 +9077,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="H269" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="270" ht="24" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
@@ -11271,14 +9109,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="H270" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="271" ht="24" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
@@ -11311,14 +9141,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
-        <v>701</v>
-      </c>
-      <c r="H271" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="272" ht="24" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
@@ -11351,14 +9173,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
-        <v>1364</v>
-      </c>
-      <c r="H272" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="273" ht="24" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
@@ -11391,14 +9205,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
-        <v>347</v>
-      </c>
-      <c r="H273" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="274" ht="24" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
@@ -11431,14 +9237,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="H274" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="275" ht="24" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
@@ -11471,14 +9269,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="H275" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="276" ht="24" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
@@ -11511,14 +9301,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="H276" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="277" ht="24" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
@@ -11551,14 +9333,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="H277" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="278" ht="24" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
@@ -11591,14 +9365,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H278" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="279" ht="24" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
@@ -11631,14 +9397,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="H279" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="280" ht="24" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
@@ -11671,14 +9429,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H280" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="281" ht="24" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
@@ -11711,14 +9461,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H281" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="282" ht="24" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
@@ -11751,14 +9493,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="H282" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="283" ht="24" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
@@ -11791,14 +9525,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="H283" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="284" ht="24" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
@@ -11831,14 +9557,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="H284" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="285" ht="24" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
@@ -11871,14 +9589,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="H285" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="286" ht="24" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
@@ -11911,14 +9621,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="H286" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="287" ht="24" customHeight="1">
       <c r="A287" s="2" t="inlineStr">
@@ -11951,14 +9653,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="H287" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="288" ht="24" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
@@ -11991,14 +9685,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="H288" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="289" ht="24" customHeight="1">
       <c r="A289" s="2" t="inlineStr">
@@ -12031,14 +9717,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="H289" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="290" ht="24" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
@@ -12071,14 +9749,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="H290" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="291" ht="24" customHeight="1">
       <c r="A291" s="2" t="inlineStr">
@@ -12111,14 +9781,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
-        <v>1040</v>
-      </c>
-      <c r="H291" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="292" ht="24" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
@@ -12151,14 +9813,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
-        <v>862</v>
-      </c>
-      <c r="H292" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="293" ht="24" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
@@ -12191,14 +9845,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="H293" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="294" ht="24" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
@@ -12231,14 +9877,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="H294" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="295" ht="24" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
@@ -12271,14 +9909,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="H295" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="296" ht="24" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
@@ -12311,14 +9941,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H296" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="297" ht="24" customHeight="1">
       <c r="A297" s="2" t="inlineStr">
@@ -12351,14 +9973,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H297" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="298" ht="24" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
@@ -12391,14 +10005,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="H298" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="299" ht="24" customHeight="1">
       <c r="A299" s="2" t="inlineStr">
@@ -12431,14 +10037,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="H299" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="300" ht="24" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
@@ -12471,14 +10069,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H300" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="301" ht="24" customHeight="1">
       <c r="A301" s="2" t="inlineStr">
@@ -12511,14 +10101,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
-        <v>209</v>
-      </c>
-      <c r="H301" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="302" ht="24" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
@@ -12551,14 +10133,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="H302" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="303" ht="24" customHeight="1">
       <c r="A303" s="2" t="inlineStr">
@@ -12591,14 +10165,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H303" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="304" ht="24" customHeight="1">
       <c r="A304" s="2" t="inlineStr">
@@ -12631,14 +10197,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
-        <v>1337</v>
-      </c>
-      <c r="H304" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="305" ht="24" customHeight="1">
       <c r="A305" s="2" t="inlineStr">
@@ -12671,14 +10229,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
-        <v>729</v>
-      </c>
-      <c r="H305" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="306" ht="24" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
@@ -12711,14 +10261,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="H306" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="307" ht="24" customHeight="1">
       <c r="A307" s="2" t="inlineStr">
@@ -12751,14 +10293,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="H307" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="308" ht="24" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
@@ -12791,14 +10325,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="H308" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="309" ht="24" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
@@ -12808,7 +10334,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Overview Stats Widget Details Click</t>
+          <t>Overview Stats Widget Redirect</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -12818,7 +10344,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Overview Stats Widget Details Click</t>
+          <t>Overview Stats Widget Redirect</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -12829,14 +10355,6 @@
       <c r="F309" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G309" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="H309" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
@@ -12871,14 +10389,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H310" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="311" ht="24" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
@@ -12911,14 +10421,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="H311" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="312" ht="24" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
@@ -12951,14 +10453,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
-        <v>844</v>
-      </c>
-      <c r="H312" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="313" ht="24" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
@@ -12991,14 +10485,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="H313" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="314" ht="24" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
@@ -13031,14 +10517,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="H314" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="315" ht="24" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
@@ -13071,14 +10549,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="H315" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="316" ht="24" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
@@ -13111,14 +10581,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="H316" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="317" ht="24" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
@@ -13151,14 +10613,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="H317" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="318" ht="24" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
@@ -13191,14 +10645,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="H318" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="319" ht="24" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
@@ -13231,14 +10677,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="H319" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="320" ht="24" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
@@ -13271,14 +10709,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="H320" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="321" ht="24" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
@@ -13311,14 +10741,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="H321" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="322" ht="24" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
@@ -13351,14 +10773,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="H322" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="323" ht="24" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
@@ -13391,14 +10805,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="H323" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="324" ht="24" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
@@ -13431,14 +10837,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H324" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="325" ht="24" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
@@ -13471,14 +10869,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="H325" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
-        </is>
-      </c>
     </row>
     <row r="326" ht="24" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
@@ -13509,14 +10899,6 @@
       <c r="F326" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-      <c r="G326" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="H326" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:40:50.911732+05:30</t>
         </is>
       </c>
     </row>
